--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7000934</v>
+        <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>91905</v>
+        <v>92382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421880</v>
+        <v>421361</v>
       </c>
       <c r="R4" t="n">
-        <v>6962152</v>
+        <v>6962635</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-08-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-08-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,31 +977,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000934</t>
+          <t>https://artportalen.se/Sighting/136814291</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91847279</v>
+        <v>7000934</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,34 +1005,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jämtlands län, Hjd</t>
+          <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421304</v>
+        <v>421880</v>
       </c>
       <c r="R5" t="n">
-        <v>6962350</v>
+        <v>6962152</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,12 +1059,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2013-08-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2013-08-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,66 +1079,66 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91847279</t>
+          <t>https://artportalen.se/Sighting/7000934</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7000936</v>
+        <v>91847279</v>
       </c>
       <c r="B6" t="n">
-        <v>92083</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1503</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Jämtlands län, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421723</v>
+        <v>421304</v>
       </c>
       <c r="R6" t="n">
-        <v>6962496</v>
+        <v>6962350</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,12 +1165,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-08-28</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-08-28</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,31 +1185,31 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000936</t>
+          <t>https://artportalen.se/Sighting/91847279</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126125633</v>
+        <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,45 +1217,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421861</v>
+        <v>421359</v>
       </c>
       <c r="R7" t="n">
-        <v>6962444</v>
+        <v>6962632</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,12 +1271,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,73 +1291,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126125633</t>
+          <t>https://artportalen.se/Sighting/136814262</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126125723</v>
+        <v>7000936</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>92083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421434</v>
+        <v>421723</v>
       </c>
       <c r="R8" t="n">
-        <v>6962287</v>
+        <v>6962496</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1393,12 +1373,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2013-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2013-08-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,73 +1393,69 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126125723</t>
+          <t>https://artportalen.se/Sighting/7000936</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348511</v>
+        <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>92455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421432</v>
+        <v>421517</v>
       </c>
       <c r="R9" t="n">
-        <v>6962635</v>
+        <v>6962248</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1503,17 +1479,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Sannolikt tidigare tretå-bohål, ca 1,6m upp i bruten gran</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,27 +1499,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348511</t>
+          <t>https://artportalen.se/Sighting/136817784</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348512</v>
+        <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>93421</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,37 +1527,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421437</v>
+        <v>421466</v>
       </c>
       <c r="R10" t="n">
-        <v>6962452</v>
+        <v>6962434</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1610,17 +1581,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1635,65 +1601,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348512</t>
+          <t>https://artportalen.se/Sighting/136817608</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126348513</v>
+        <v>136814545</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421488</v>
+        <v>421334</v>
       </c>
       <c r="R11" t="n">
-        <v>6962412</v>
+        <v>6962668</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1717,17 +1683,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,65 +1703,65 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348513</t>
+          <t>https://artportalen.se/Sighting/136814545</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126348514</v>
+        <v>136814598</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>79476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421522</v>
+        <v>421373</v>
       </c>
       <c r="R12" t="n">
-        <v>6962292</v>
+        <v>6962696</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,17 +1785,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,65 +1805,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348514</t>
+          <t>https://artportalen.se/Sighting/136814598</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126348515</v>
+        <v>136817581</v>
       </c>
       <c r="B13" t="n">
-        <v>57953</v>
+        <v>79476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421542</v>
+        <v>421464</v>
       </c>
       <c r="R13" t="n">
-        <v>6962275</v>
+        <v>6962438</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1931,17 +1887,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,65 +1907,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348515</t>
+          <t>https://artportalen.se/Sighting/136817581</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126348516</v>
+        <v>136818208</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421720</v>
+        <v>421365</v>
       </c>
       <c r="R14" t="n">
-        <v>6962266</v>
+        <v>6962301</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2038,17 +1989,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,27 +2009,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348516</t>
+          <t>https://artportalen.se/Sighting/136818208</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126348517</v>
+        <v>136814517</v>
       </c>
       <c r="B15" t="n">
-        <v>57953</v>
+        <v>78879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,37 +2037,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421753</v>
+        <v>421325</v>
       </c>
       <c r="R15" t="n">
-        <v>6962274</v>
+        <v>6962635</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2145,17 +2091,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2170,65 +2111,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348517</t>
+          <t>https://artportalen.se/Sighting/136814517</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126348518</v>
+        <v>136817830</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>80595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421794</v>
+        <v>421511</v>
       </c>
       <c r="R16" t="n">
-        <v>6962250</v>
+        <v>6962253</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2252,17 +2193,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2277,24 +2213,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348518</t>
+          <t>https://artportalen.se/Sighting/136817830</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126348519</v>
+        <v>126125633</v>
       </c>
       <c r="B17" t="n">
         <v>57953</v>
@@ -2323,19 +2259,27 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421839</v>
+        <v>421861</v>
       </c>
       <c r="R17" t="n">
-        <v>6962191</v>
+        <v>6962444</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2359,17 +2303,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2384,24 +2323,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348519</t>
+          <t>https://artportalen.se/Sighting/126125633</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126348520</v>
+        <v>126125723</v>
       </c>
       <c r="B18" t="n">
         <v>57953</v>
@@ -2430,19 +2369,27 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421846</v>
+        <v>421434</v>
       </c>
       <c r="R18" t="n">
-        <v>6962154</v>
+        <v>6962287</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2466,17 +2413,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2491,24 +2433,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348520</t>
+          <t>https://artportalen.se/Sighting/126125723</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126348521</v>
+        <v>126348511</v>
       </c>
       <c r="B19" t="n">
         <v>57953</v>
@@ -2537,16 +2479,24 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421869</v>
+        <v>421432</v>
       </c>
       <c r="R19" t="n">
-        <v>6962131</v>
+        <v>6962635</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,7 +2533,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Sannolikt tidigare tretå-bohål, ca 1,6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,13 +2559,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348521</t>
+          <t>https://artportalen.se/Sighting/126348511</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126348522</v>
+        <v>126348512</v>
       </c>
       <c r="B20" t="n">
         <v>57953</v>
@@ -2650,10 +2600,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421895</v>
+        <v>421437</v>
       </c>
       <c r="R20" t="n">
-        <v>6962187</v>
+        <v>6962452</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,7 +2640,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2716,13 +2666,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348522</t>
+          <t>https://artportalen.se/Sighting/126348512</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126348523</v>
+        <v>126348513</v>
       </c>
       <c r="B21" t="n">
         <v>57953</v>
@@ -2757,10 +2707,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421904</v>
+        <v>421488</v>
       </c>
       <c r="R21" t="n">
-        <v>6962234</v>
+        <v>6962412</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,7 +2747,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2823,13 +2773,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348523</t>
+          <t>https://artportalen.se/Sighting/126348513</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126348524</v>
+        <v>126348514</v>
       </c>
       <c r="B22" t="n">
         <v>57953</v>
@@ -2864,10 +2814,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421923</v>
+        <v>421522</v>
       </c>
       <c r="R22" t="n">
-        <v>6962232</v>
+        <v>6962292</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,13 +2880,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348524</t>
+          <t>https://artportalen.se/Sighting/126348514</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126348525</v>
+        <v>126348515</v>
       </c>
       <c r="B23" t="n">
         <v>57953</v>
@@ -2971,10 +2921,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>422007</v>
+        <v>421542</v>
       </c>
       <c r="R23" t="n">
-        <v>6962244</v>
+        <v>6962275</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,13 +2987,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348525</t>
+          <t>https://artportalen.se/Sighting/126348515</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126348526</v>
+        <v>126348516</v>
       </c>
       <c r="B24" t="n">
         <v>57953</v>
@@ -3078,10 +3028,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421990</v>
+        <v>421720</v>
       </c>
       <c r="R24" t="n">
-        <v>6962251</v>
+        <v>6962266</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,13 +3094,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348526</t>
+          <t>https://artportalen.se/Sighting/126348516</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126348527</v>
+        <v>126348517</v>
       </c>
       <c r="B25" t="n">
         <v>57953</v>
@@ -3185,10 +3135,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421924</v>
+        <v>421753</v>
       </c>
       <c r="R25" t="n">
-        <v>6962309</v>
+        <v>6962274</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,13 +3201,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348527</t>
+          <t>https://artportalen.se/Sighting/126348517</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126348528</v>
+        <v>126348518</v>
       </c>
       <c r="B26" t="n">
         <v>57953</v>
@@ -3292,10 +3242,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421918</v>
+        <v>421794</v>
       </c>
       <c r="R26" t="n">
-        <v>6962269</v>
+        <v>6962250</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3358,13 +3308,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348528</t>
+          <t>https://artportalen.se/Sighting/126348518</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126348529</v>
+        <v>126348519</v>
       </c>
       <c r="B27" t="n">
         <v>57953</v>
@@ -3399,10 +3349,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421911</v>
+        <v>421839</v>
       </c>
       <c r="R27" t="n">
-        <v>6962272</v>
+        <v>6962191</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3465,13 +3415,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348529</t>
+          <t>https://artportalen.se/Sighting/126348519</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126348530</v>
+        <v>126348520</v>
       </c>
       <c r="B28" t="n">
         <v>57953</v>
@@ -3506,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421907</v>
+        <v>421846</v>
       </c>
       <c r="R28" t="n">
-        <v>6962257</v>
+        <v>6962154</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,7 +3496,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3572,13 +3522,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348530</t>
+          <t>https://artportalen.se/Sighting/126348520</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126348531</v>
+        <v>126348521</v>
       </c>
       <c r="B29" t="n">
         <v>57953</v>
@@ -3613,10 +3563,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421867</v>
+        <v>421869</v>
       </c>
       <c r="R29" t="n">
-        <v>6962255</v>
+        <v>6962131</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3653,7 +3603,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3679,13 +3629,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348531</t>
+          <t>https://artportalen.se/Sighting/126348521</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126348532</v>
+        <v>126348522</v>
       </c>
       <c r="B30" t="n">
         <v>57953</v>
@@ -3720,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421731</v>
+        <v>421895</v>
       </c>
       <c r="R30" t="n">
-        <v>6962317</v>
+        <v>6962187</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3760,7 +3710,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3786,13 +3736,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348532</t>
+          <t>https://artportalen.se/Sighting/126348522</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126348542</v>
+        <v>126348523</v>
       </c>
       <c r="B31" t="n">
         <v>57953</v>
@@ -3827,10 +3777,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>421390</v>
+        <v>421904</v>
       </c>
       <c r="R31" t="n">
-        <v>6962623</v>
+        <v>6962234</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,7 +3817,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3893,16 +3843,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348542</t>
+          <t>https://artportalen.se/Sighting/126348523</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126133773</v>
+        <v>126348524</v>
       </c>
       <c r="B32" t="n">
-        <v>79917</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,40 +3860,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>421831</v>
+        <v>421923</v>
       </c>
       <c r="R32" t="n">
-        <v>6962414</v>
+        <v>6962232</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3967,12 +3914,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3981,23 +3933,1539 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348524</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126348525</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>422007</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6962244</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348525</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126348526</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>421990</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6962251</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348526</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126348527</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>421924</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6962309</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348527</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126348528</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>421918</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6962269</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348528</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126348529</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>421911</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6962272</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348529</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126348530</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>421907</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6962257</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348530</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126348531</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>421867</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6962255</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348531</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126348532</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>421731</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6962317</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348532</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126348542</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>421390</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6962623</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348542</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136814343</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Över Dammtjärn, Abborrsjön,Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>421350</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6962652</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814343</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136814581</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>421348</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6962696</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814581</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136817411</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>421391</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6962564</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136817411</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136818382</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>421494</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6962506</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136818382</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126133773</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>421831</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6962414</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126133773</t>
         </is>
@@ -4036,6 +5504,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92455</v>
+        <v>92457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92457</v>
+        <v>92459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>136814545</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136814598</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136817581</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136818208</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136814517</v>
       </c>
       <c r="B15" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136817830</v>
       </c>
       <c r="B16" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92459</v>
+        <v>92461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>136814545</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136814598</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136817581</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136818208</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136814517</v>
       </c>
       <c r="B15" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136817830</v>
       </c>
       <c r="B16" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92461</v>
+        <v>92462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>136814545</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136814598</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136817581</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136818208</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136814517</v>
       </c>
       <c r="B15" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136817830</v>
       </c>
       <c r="B16" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92462</v>
+        <v>92468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92468</v>
+        <v>92472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>136814545</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136814598</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136817581</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136818208</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136814517</v>
       </c>
       <c r="B15" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136817830</v>
       </c>
       <c r="B16" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92472</v>
+        <v>92474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>136814545</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136814598</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136817581</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136818208</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136814517</v>
       </c>
       <c r="B15" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136817830</v>
       </c>
       <c r="B16" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92474</v>
+        <v>92487</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>136814545</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136814598</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136817581</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136818208</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136814517</v>
       </c>
       <c r="B15" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136817830</v>
       </c>
       <c r="B16" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>136814343</v>
       </c>
       <c r="B42" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>136814581</v>
       </c>
       <c r="B43" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>136817411</v>
       </c>
       <c r="B44" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136818382</v>
       </c>
       <c r="B45" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92487</v>
+        <v>92489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>136814545</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136814598</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136817581</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136818208</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136814517</v>
       </c>
       <c r="B15" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136817830</v>
       </c>
       <c r="B16" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>136814343</v>
       </c>
       <c r="B42" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>136814581</v>
       </c>
       <c r="B43" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>136817411</v>
       </c>
       <c r="B44" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136818382</v>
       </c>
       <c r="B45" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -4948,11 +4948,7 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Över Dammtjärn, Abborrsjön,Storsjö, Hjd</t>
@@ -5060,11 +5056,7 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
@@ -5172,11 +5164,7 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>
@@ -5284,11 +5272,7 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Neder-Dammtjärnen, Neder-Dammtjärnen, Hjd</t>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92489</v>
+        <v>92492</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92492</v>
+        <v>92502</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>136814545</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136814598</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136817581</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136818208</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136814517</v>
       </c>
       <c r="B15" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136817830</v>
       </c>
       <c r="B16" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>136814343</v>
       </c>
       <c r="B42" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>136814581</v>
       </c>
       <c r="B43" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>136817411</v>
       </c>
       <c r="B44" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>136818382</v>
       </c>
       <c r="B45" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92502</v>
+        <v>92503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92503</v>
+        <v>92506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>136814545</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136814598</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136817581</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136818208</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136814517</v>
       </c>
       <c r="B15" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136817830</v>
       </c>
       <c r="B16" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>136814343</v>
       </c>
       <c r="B42" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>136814581</v>
       </c>
       <c r="B43" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>136817411</v>
       </c>
       <c r="B44" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>136818382</v>
       </c>
       <c r="B45" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92506</v>
+        <v>92508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136814291</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136814262</v>
       </c>
       <c r="B7" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>136817784</v>
       </c>
       <c r="B9" t="n">
-        <v>92508</v>
+        <v>92513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136817608</v>
       </c>
       <c r="B10" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>136814545</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136814598</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136817581</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136818208</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>136814517</v>
       </c>
       <c r="B15" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>136817830</v>
       </c>
       <c r="B16" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>136814343</v>
       </c>
       <c r="B42" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>136814581</v>
       </c>
       <c r="B43" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>136817411</v>
       </c>
       <c r="B44" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>136818382</v>
       </c>
       <c r="B45" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
